--- a/logs/run_log.xlsx
+++ b/logs/run_log.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -760,7 +760,6 @@
       <c r="AC2" t="n">
         <v>3.876</v>
       </c>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>v0.9</t>
@@ -780,6 +779,9093 @@
         <is>
           <t>What is the difference between a family and the individuals who make it up?
 Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bb888fee-ce45-45aa-9dc1-ba30d44a3fa6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:26:31+00:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A family is a relational system defined by emotional bonds, shared roles, and shared history, which exists as a distinct unit beyond any single member. Each individual within a family retains their own autonomy, identity, and personal experiences, which differ from the collective dynamics and shared bonds that define the family as a whole.</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>341</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>844</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>882</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>160.728</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>e0647caa-0d63-4b89-b8ab-744671c86e5c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:29:44+00:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>A family is more than the sum of its members; it is a relational system defined by shared histories, roles, values, and emotional bonds that create a distinct identity and set of patterns of interaction. The individuals within it retain their own personalities, goals, and agency, but when they participate in the family they negotiate, reinforce, or transform those collective dynamics. Thus the family exists as a relational whole, while each person remains a separate, autonomous subject within that whole.</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>509</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>131</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>218</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11.133</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>c451e91c-c227-4c14-aa4e-2439f3efbd83</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:29:44+00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A family is a relational system with its own dynamics, norms, and collective identity that emerges from the interactions of its members, not merely the individuals themselves. While each person brings unique traits and autonomy, the family functions as an interconnected unit where roles, bonds, and shared experiences shape both the group and the individuals within it.</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>370</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>521</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>559</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12.344</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>c82a9096-5167-4a26-9c66-18c9d8135013</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:29:57+00:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A family is a relational system—a set of roles, histories, shared meanings, and obligations that bind its members together and shape how they interact with the wider world. The individuals within it retain their own personalities, preferences, and life courses, which may align with, resist, or transform the family’s patterns. In short, the family is the network and narrative that emerges from the people, while the people are the distinct, autonomous beings who compose and continuously redefine that network.</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>512</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>159</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>246</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.421</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>632fcc9e-34b4-4011-9403-b28b7dbd6691</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:29:57+00:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A family is not merely a collection of individuals but a relational system defined by shared bonds, roles, and histories that emerge between its members. While each person retains their own identity, thoughts, and autonomy, the family creates a collective dynamic that shapes how those individuals understand themselves and interact with the world. Thus, the difference lies in the distinction between personal identity and the interconnected, systemic whole formed by those individuals.</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>487</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>556</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>594</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d828cf81-5550-4bbc-8978-7e0703d74fe2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:30:11+00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A family is a relational system—a network of roles, histories, expectations, and shared meanings that links its members together and shapes how they act in the world. The individuals who make it up retain their own personalities, desires, and agency, which may align with, conflict with, or transform the family’s collective identity. In short, the family is the emergent whole created by the ongoing interactions of its members, while each member remains a distinct, self‑directed person.</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>489</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>168</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>255</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.401</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bd12227d-adaa-46ac-b11c-ceb07b1b2a43</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:30:11+00:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A family is a relational unit defined by shared bonds, roles, and interdependence, while individuals are autonomous persons with their own identities and experiences. The difference lies in how the family creates a collective dynamic that is more than just the sum of its members, shaping and being shaped by each person within it. Thus, individuals provide the people, but the family provides the connections and structure that give it its unique character.</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>458</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>587</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>625</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>17.092</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ffe28060-24e4-4429-99f6-1ff146d34228</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:30:28+00:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A family is a relational system—a network of roles, histories, norms, and shared identities that creates interdependence and a sense of belonging among its members. The individuals who make it up retain their own personalities, desires, and agency, but when they interact within the family they become more than the sum of those parts, shaping and being shaped by the family’s collective dynamics. In short, a family is the connective structure and cultural context; the individuals are the autonomous people who populate and animate that structure.</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>549</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>186</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>273</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.563</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>c9b00f33-7407-4775-ab49-12b8c34023cd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:30:28+00:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A family functions as a relational system with its own dynamics, roles, and shared patterns of interaction that exist independently of any single member. While individuals bring their own unique identities, needs, and life experiences, the family creates a collective context that shapes and is shaped by those individuals over time. In essence, the difference lies in the emergent relationships and structural bonds that define the family, which are more than the sum of its parts.</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>482</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>576</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>614</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>24.423</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4282fb0f-8f9c-4a1e-b288-a3ce7da6a669</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:30:53+00:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A family is a social unit defined by shared relationships, responsibilities, and a collective identity that shapes how its members interact, support one another, and perceive the world. The individuals within it retain distinct personalities, preferences, and life stories, but when they form a family their actions and meanings become intertwined, creating patterns of interdependence and cultural meaning that go beyond each person’s isolated experience. In short, a family is the emergent whole‑system of connections and roles, while its members are the separate people who give that system its substance.</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>608</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>197</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>284</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12.392</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eac3d3ca-ba37-4944-824e-e7a3c17bd778</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:30:53+00:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A family is a relational system defined by emotional bonds, shared roles, and interconnected dynamics, whereas individuals are autonomous beings with distinct identities and needs. The key difference is that a family emerges from the relationships between people, creating a collective whole with its own patterns, history, and purpose that cannot be reduced to the sum of its members. Thus, while individuals exist independently, a family exists as a functional unit whose nature is shaped by how its members relate to one another.</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>532</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>681</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>719</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14.664</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7c532a04-f72e-4d27-96c6-912a87e6c044</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:08+00:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A family is the social system that binds its members together through shared history, roles, responsibilities, and often legal or cultural ties, creating a collective identity that functions as a unit in society. The individuals within it, by contrast, retain their own personalities, aspirations, and personal experiences, which may align with or differ from the family’s shared values and expectations. In short, the family is the relational network and purpose‑driven whole, while the individuals are the distinct persons who compose and give it life.</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>554</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>189</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>276</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.063</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9696ff00-0323-4f5e-a97e-0e843ce22a97</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:08+00:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A family is a relational unit defined by emotional bonds, shared roles, and interdependence, rather than merely a collection of separate people. The individuals within it retain their own identities, autonomy, and personal experiences, which exist independently of the family structure. The key difference, then, is that a family creates emergent dynamics, norms, and a collective identity that exist between and among the members, not within any one of them alone.</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>465</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>695</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>733</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>48880730-88c7-4434-9744-b38cb1a02d0d</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:23+00:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A family is the relational network that gives its members shared roles, histories, expectations and a collective identity—something that exists as a social unit regardless of any single person’s presence. The individuals inside it, by contrast, retain their own personalities, experiences, and autonomy, each contributing to but also standing apart from the family’s overarching pattern. In short, the family is the structure and meaning created by the members’ interconnections, while the members are the distinct, self‑contained agents who populate that structure.</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>566</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>139</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>226</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.598</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bc88c633-979a-4566-b242-657433ef638f</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:23+00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A family is a social unit defined by relationships, bonds, and shared responsibilities, whereas individuals are separate people with their own identities. The difference is that a family emerges from how those individuals interact, communicate, and depend on one another, creating something more complex than just a group of people. Thus, while individuals bring their unique traits, the family itself is shaped by those traits plus the patterns, rules, and emotional connections that exist between them.</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>504</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>706</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>744</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.468</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2ab1d16d-1b50-4187-943e-83b4620debaa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:32+00:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A family is a relational system—a set of shared histories, roles, expectations, and emotional bonds that creates a collective identity and functions as a unit. The individuals who make it up retain their own separate personalities, goals, and experiences, and they can exist outside of that system. In short, the family is the network that gives meaning to the connections; the individuals are the distinct people who occupy those connections.</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>443</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>146</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>233</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>b76718ec-2a04-48f7-9551-cf89f3a180d5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:32+00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A family is a relational unit formed by individuals connected through blood, marriage, or choice, characterized by shared bonds, roles, and interdependence. While each individual possesses their own identity, autonomy, and personal experiences, the family itself exists as a distinct social system where the connections between members create dynamics and meanings that go beyond the sum of its parts. Therefore, the difference lies in the shift from individual independence to collective relationship and shared identity.</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>522</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>678</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>716</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>18.898</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>313a435e-33a0-4fd0-a950-24c05be0e4cd</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:51+00:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>determinism</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A family is the relational network that gives its members shared identity, history, and mutual responsibilities, shaping how they interact and are perceived by the world. The individuals within it retain their own personalities, desires, and agency, which may align with, diverge from, or even challenge the family’s collective narrative. Thus, the family is the emergent social unit, while its members are the distinct persons who compose—and sometimes reshape—it.</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>465</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>124</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>211</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.804</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ad971dd2-8046-4533-affc-d8e440a63e68</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:31:51+00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>determinism</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A family is a relational system defined by bonds, roles, and shared context, whereas the individuals within it each have their own independent identities and autonomy. The family emerges from the interactions and connections between these people, creating a collective dynamic that exists beyond any single member. In essence, a family is the pattern of relationship, while the individuals are the people who form it.</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>417</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>604</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>642</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>15.334</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>766677b2-0494-471f-a400-f42a6ba28e9a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Yes—property can be owned by a family, though the ownership must be held by one or more legal persons (such as the spouses, parents, or adult children) who are named on the title. In many jurisdictions families use joint‑tenancy, tenancy‑in‑common, community‑property rules, or a family trust to hold the deed collectively. The exact mechanics vary by state or country, but the law permits a family group to own and manage real or personal property together.</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>458</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>215</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>293</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.244</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>804ca063-6934-457d-afa5-910c15a91943</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically through legal arrangements like joint ownership, a tenancy in common, or a family trust. These structures specify how the property is held, transferred, and managed among family members. This allows families to retain control and pass ownership to future generations.</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>309</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>640</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>669</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.659</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dba82958-aaaa-411d-b8fe-29ff3bbc026e</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:34:59+00:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, but it must be held by legal owners—typically the individual family members or a legal entity such as a trust or limited liability company created for that purpose. In practice families often use joint‑tenancy, tenancy‑in‑common, or a family trust to share ownership and simplify transfer or management of the asset.</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>348</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>155</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>233</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.745</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5cbf0f28-d50d-41e8-991a-afab7f4c0a73</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:34:59+00:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property. Families often hold title jointly, as tenants in common, or through legal structures like family trusts. These arrangements allow shared ownership, rights, and responsibilities for real estate or other assets.</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>241</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>458</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>487</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.513</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7a54e639-085b-459b-8d57-57ec8d103a16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:10+00:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Yes. In most jurisdictions a family can hold title to real or personal property—either collectively as joint tenants or tenants‑in‑common, or through a family trust, corporation, or other legal entity. The exact form and rights depend on the local property‑ownership laws and how the family structures the ownership.</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>316</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>121</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>199</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.387</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1e0fcce3-fb24-407d-9177-a6ada10f6b75</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:10+00:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically through joint ownership, trusts, or as a legal entity depending on the jurisdiction. Ownership may be structured as tenants in common, joint tenants, or via a family trust to manage rights, responsibilities, and inheritance.</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>266</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>354</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>383</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>6.449</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>954fc67e-8152-4974-95e1-4b6375f66d05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:17+00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically by holding title in the name of one or more family members (e.g., as joint tenants, tenants in common, or via a family trust). The ownership structure determines how the property is transferred, taxed, and how decision‑making authority is shared among the family members.</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>313</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>103</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>181</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.217</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>496572e9-04b4-4261-956a-680702f68a7b</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:17+00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either individually or jointly through legal arrangements like joint tenancy or tenancy in common. Families frequently purchase homes or land together, and many also use trusts, LLCs, or other entities to manage ownership, liability, and succession. Property laws vary by jurisdiction, but in most places, family ownership of real estate is fully recognized and protected.</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>404</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>534</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>563</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.829000000000001</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2b1a21de-61cc-4f7c-bd9f-855b55075d86</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:27+00:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Yes. In most jurisdictions a family can hold title to real or personal property together—often as joint tenants, tenants in common, or through a family trust or LLC. The exact legal structure and rights of each member depend on local property and inheritance laws.</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>264</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>135</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>213</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.577</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8f154e1b-f575-40ad-b145-327f252c177f</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:27+00:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either directly as joint owners or through legal structures like trusts and corporations. This arrangement allows them to collectively manage, use, and transfer the property according to their agreed terms.</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>238</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>381</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>410</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30bac673-6ec2-42ec-9649-d2ba8664ca8b</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:52+00:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, often through joint ownership, tenancy in common, or a family trust. This arrangement allows multiple family members to hold shared rights to assets like a home or land, with legal frameworks varying by jurisdiction but generally recognizing family property ownership.</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>374</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>403</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.624</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>70b8a9c8-2bf9-41df-9fc0-d4f978a94146</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:52+00:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, but the ownership must be held by one or more legally recognized owners—such as individual family members, a married couple, a trust, an LLC, or another entity that the family establishes. The family’s interest is expressed through how those owners hold title (e.g., joint tenancy, tenancy in common, or a family trust), rather than through an abstract “family” entity.</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>401</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>156</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>234</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1266fb21-005f-4419-8c29-0d0eef55e1d4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:57+00:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either as individual co-owners or through legal structures like a trust or partnership. Ownership can be structured as joint tenancy, tenancy in common, or held by a family entity, depending on local laws and the family's objectives. These arrangements affect rights of possession, inheritance, and tax treatment, so families often seek legal or financial advice when acquiring property.</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>419</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>514</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>543</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.499</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0d32b19a-63c1-47d1-9ef1-6db022be253d</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:35:57+00:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Yes—property can be held in the name of a family as a legal owner, but the ownership must be structured through a recognized legal entity (such as a joint tenancy, tenancy‑in‑common, partnership, LLC, trust, or a corporation). In practice, the family members are either co‑owners with defined shares or beneficiaries of a trust that holds title, giving the family collectively the rights to use, sell, or bequeath the property.</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>427</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>151</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>229</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.094</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>24cb8e46-cd47-4b0c-b30b-7a1412febefb</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:36:04+00:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Yes. A family can hold title to real or personal property, typically by owning it jointly (e.g., as tenants‑in‑common or joint tenants with right of survivorship) or through a legal entity such as a trust or limited liability company set up for the family’s use. The specific ownership structure determines each member’s rights, obligations, and how the property passes on after death.</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>385</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>124</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>202</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bac89ee7-54d5-4493-99a1-45497ab99148</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:36:04+00:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property. Families can hold title to real estate jointly, as tenants in common, or through a family trust, allowing multiple people to share ownership rights and responsibilities. This is legally recognized in most countries and can help with estate planning, tax benefits, and preserving assets across generations.</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>337</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>529</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>558</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>10.419</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>28e1f7f6-ac21-462b-ba4f-cfc19100bcbb</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:36:15+00:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Yes—property can be owned by a family, but the ownership must be held in a legally recognized name such as a joint tenancy among family members, a trust, an LLC, or another entity created for that purpose. In most jurisdictions the law treats the individual owners (e.g., spouses, parents, or adult children) as co‑owners, while the “family” itself isn’t a separate legal person unless you formalize it through a trust or corporation.</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>434</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>277</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.092</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>33703aa7-4c2d-4db6-a664-130d69efcd2e</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:36:15+00:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically through joint ownership, a family trust, or as co-owners holding title together. The specific legal structure—such as joint tenancy, tenancy in common, or a family LLC—determines how ownership is held, transferred, and taxed. Laws vary by jurisdiction, but in most places, families have clear legal pathways to acquire, hold, and inherit real estate or other property.</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>410</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>684</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>713</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.899</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1637f3b1-5a17-4f1e-9adc-e640c42d8e83</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:36:19+00:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>determinism</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Yes—families can own real or personal property, but the ownership must be held in a legally recognized form such as joint tenancy, tenancy‑in‑common, a family trust, or a corporation. The specific structure determines how the title is recorded, how decisions are made, and how the property passes on after death. In practice, many families use trusts or joint ownership agreements to simplify management and estate planning.</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>424</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>232</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.227</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>e63b9197-2e03-4f44-985d-3924c709b45e</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:36:19+00:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>determinism</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property through various legal arrangements such as joint ownership, tenancy in common, or a family trust. These structures allow multiple family members to hold title, share responsibilities, and manage the asset according to agreed terms. Ownership rules and tax implications may vary depending on local laws and the specific arrangement chosen.</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>369</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>482</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>511</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>27391c88-d568-4702-94b9-12a01cf04ccc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:18+00:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Yes. A family can hold title to real or personal property by owning it jointly—through forms such as tenancy‑in‑common, joint tenancy with right of survivorship, or, in some states, community‑property arrangements. Often families also use legal vehicles like trusts, limited‑liability companies, or family limited partnerships to own and manage the assets together.</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>158</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>236</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>29a28869-de65-42e9-8675-add6764a4054</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:18+00:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property legally, often through joint ownership, tenancy in common, or a family trust. This allows multiple family members to hold title together, manage the asset, and pass it down according to their wishes. Ownership structures vary by jurisdiction, but the concept of a family holding property is widely recognized and protected.</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>354</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>542</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>571</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>13.504</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>a3ffc6de-b555-4e5d-bcb8-208898094fb3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:32+00:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Yes. A family can hold title to real‑estate or other assets, typically by having the individual members listed as co‑owners (e.g., joint tenants or tenants in common) or by placing the property in a family‑named entity such as a trust, partnership, LLC, or corporation. The specific ownership structure determines how the property is managed, transferred, and taxed.</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>366</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>223</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.453</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>77167ef8-51f9-4eec-a564-04914e3103b7</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:32+00:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either jointly or through legal structures like trusts, partnerships, or corporations. These arrangements allow families to manage, use, and pass down real estate or other assets while defining ownership shares, rights, and responsibilities according to local laws.</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>297</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>692</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>721</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.108</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2c3b00c3-25b9-4df1-9626-712afac136e2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:39+00:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Yes, a family can own real or personal property, but the ownership must be held in a recognized legal form—such as joint tenancy, tenancy‑in‑common, a trust, or a family‑run business entity—so that the law can identify who holds title. The specific structure used depends on the jurisdiction’s property and estate laws and on the family’s goals for control, inheritance, and tax planning.</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>388</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>172</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1762b762-b0cd-4ad5-a8b8-5f2e3b0a73ec</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:39+00:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either jointly or through legal arrangements like trusts or tenancy in common. Such ownership may involve a family home, investment real estate, or land held collectively for familial use and benefit.</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>232</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>491</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>520</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>10.049</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>f9a626d7-071b-4a42-a723-92ac990bc248</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:50+00:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Yes, a family can hold title to real‑estate, but the ownership must be in the name of legally recognized owners—such as spouses, adult children, or a legal entity (e.g., a family trust, LLC, or partnership) that the family creates. In practice, families often use joint‑tenancy, tenancy‑in‑common, or community‑property arrangements, or they place the property in a trust that is administered for the benefit of family members.</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>427</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>268</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>c4208401-3986-4e08-9d90-d14e71b08180</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:37:50+00:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically through joint ownership, a family trust, or a legal entity like a family LLC. Ownership can be structured so that multiple family members hold shared rights, responsibilities, and benefits, often with specific agreements governing transfer, use, or succession. Laws regarding family property ownership vary by jurisdiction, but the general principle allows families to hold and manage real estate or other assets collectively.</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>468</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>648</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>677</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>17.657</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>a6734254-ab44-40c5-8f03-5236519e4787</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:38:08+00:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically by holding title in the names of multiple family members (e.g., joint tenancy or tenancy‑in‑common) or through a family‑run entity such as a trust, partnership, LLC, or corporation. The exact form of ownership and the rights and responsibilities of each family member depend on the jurisdiction’s property and estate laws. Using a structured entity can simplify management, inheritance planning, and liability protection.</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>463</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>158</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>236</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6da02ffc-1f1c-466c-baa1-98b1db3eda67</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:38:08+00:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, often holding title jointly through legal structures like tenancy in common or joint tenancy. Families commonly purchase homes or land together for residence, investment, or to keep property within the family, and such arrangements can be managed through ownership agreements or trusts.</t>
+        </is>
+      </c>
+      <c r="Y51" t="n">
+        <v>318</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>587</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>616</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>27.351</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>b0fae87b-7d9e-4382-b785-2779b92ffebd</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:38:35+00:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Yes. A family can hold title to real or personal property in its own name—either as a joint tenancy, tenancy‑in‑common, or through a legal entity such as a family trust or partnership that the members create. The exact form depends on the jurisdiction’s property‑ownership laws and the family’s objectives (e.g., ease of transfer, tax planning, creditor protection).</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>366</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>188</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>87f28e35-fba9-4b27-ad85-1fdd9cb0be51</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:38:35+00:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either individually or collectively through legal arrangements like joint tenancy or tenancy in common. Such ownership allows family members to share rights, responsibilities, and benefits associated with the property.</t>
+        </is>
+      </c>
+      <c r="Y53" t="n">
+        <v>250</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>446</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>475</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.061</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>57aec270-4122-488f-96c6-cf4aefaa47d6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:38:46+00:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V54" t="b">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Yes. A family can hold title to real‑estate or other assets, typically by having the members own it jointly (e.g., as joint tenants with right of survivorship or tenants in common) or by placing it in a family‑run entity such as a trust, partnership, LLC, or corporation. The specific ownership structure is chosen to suit the family’s goals for control, inheritance, tax planning, and liability protection.</t>
+        </is>
+      </c>
+      <c r="Y54" t="n">
+        <v>407</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>238</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bd2bd3c8-54fe-4cb0-b10d-96f0c0aba29b</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:38:46+00:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V55" t="b">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically through joint ownership, a family trust, or as co-owners under local law. Ownership may be structured as tenants in common, joint tenancy, or held by a legal entity like a limited liability company to manage shared assets and responsibilities. These arrangements allow families to pool resources, pass property to future generations, and define rights and obligations through formal agreements or estate planning.</t>
+        </is>
+      </c>
+      <c r="Y55" t="n">
+        <v>455</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>627</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>656</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3575e57a-69ca-4e8d-9759-395b577dc085</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:39:05+00:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Yes. In most jurisdictions a group of related individuals can hold title to real‑estate together—typically as joint tenants, tenants‑in‑common, or through a family‑run entity such as a trust, partnership, or LLC. The ownership structure determines each member’s rights, survivorship rules, and how the property is transferred or taxed.</t>
+        </is>
+      </c>
+      <c r="Y56" t="n">
+        <v>335</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>144</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5fcea36d-935c-402f-a030-5b67ac7a95eb</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:39:05+00:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, either jointly or as individuals, depending on the legal structure and jurisdiction. Property can be held in the names of family members collectively, such as through joint tenancy, tenancy in common, or via a family trust or LLC. This allows families to manage, transfer, and protect assets together, though specific rights and responsibilities vary by local laws and ownership agreements.</t>
+        </is>
+      </c>
+      <c r="Y57" t="n">
+        <v>422</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>619</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>648</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>33.905</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5ead0b56-ff49-4eab-80df-28499e0da3b2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:39:39+00:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>determinism</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V58" t="b">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Yes—families can own real or personal property, typically by holding title in the names of one or more family members, as joint tenants, tenants‑in‑common, or through a family trust or corporation. The specific ownership structure is chosen to suit the family’s goals for control, inheritance planning, and tax treatment.</t>
+        </is>
+      </c>
+      <c r="Y58" t="n">
+        <v>321</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>127</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>205</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>5.671</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>5e9a2654-9202-475f-802f-c5a234eab2da</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:39:39+00:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>K-K1b-EN</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>K-K1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>determinism</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V59" t="b">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Yes, a family can own property, typically through joint ownership, a family trust, or as co-owners on a title. Ownership structures vary by jurisdiction but generally allow families to hold real estate or other assets together for shared use, investment, or estate planning purposes. This arrangement can provide legal, financial, and practical benefits depending on the family's goals and local laws.</t>
+        </is>
+      </c>
+      <c r="Y59" t="n">
+        <v>401</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>737</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>766</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>7.889</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Can a family own property?</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Can a family own property?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>b1d0a92c-33e6-4752-b470-488c8b1eb2d5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:43:09+00:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V60" t="b">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A family is the relational network and collective identity that binds its members—through kinship, shared history, values, and mutual responsibilities—creating a social unit that functions as a whole. The individuals who make up that family, however, remain distinct persons with their own thoughts, feelings, and personal agency, each contributing to but not wholly defined by the family’s collective role. In short, the family is the connective structure and shared context, while its members are the separate, autonomous people who populate it.</t>
+        </is>
+      </c>
+      <c r="Y60" t="n">
+        <v>547</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>185</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>272</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>697d52ac-4fa1-4f70-aece-b434183fb89e</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:43:09+00:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>K-C1a-EN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>K-C1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>contrastive</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>brief-v1</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Answer in two or three sentences.</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V61" t="b">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A family is a relational unit whose identity and function emerge from the connections, shared history, and interdependence among its members, rather than from any individual alone. While each individual possesses their own autonomy, thoughts, and personal identity, the family creates a distinct social dynamic—roles, bonds, and collective experiences—that wouldn't exist in isolation. Thus, the difference lies in how relationships transform a group of people into a cohesive system with its own pattern of interaction and meaning.</t>
+        </is>
+      </c>
+      <c r="Y61" t="n">
+        <v>532</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>710</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>748</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>10.352</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>What is the difference between a family and the individuals who make it up?
+Answer in two or three sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7d0406fb-89ed-47ec-afa7-7a5aee6d885f</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:45:58+00:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V62" t="b">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Sure! Here are ten influential philosophers from different eras and traditions, along with a brief note about each of them:
+| # | Philosopher | Era &amp; Region | Key Contribution / Famous Work |
+|---|--------------|--------------|---------------------------------|
+| 1 | **Socrates** | 5th c. BC, Ancient Greece | The “Socratic method” of questioning; known only through the dialogues of his student Plato. |
+| 2 | **Plato** | 4th c. BC, Ancient Greece | Founder of the Academy; author of *The Republic*, *Phaedo*, *Symposium*, etc. |
+| 3 | **Aristotle** | 4th c. BC, Ancient Greece | Systematized logic, metaphysics, ethics, and natural science; wrote *Nicomachean Ethics* and *Metaphysics*. |
+| 4 | **Immanuel Kant** | 18th c., Germany | Developed transcendental idealism and the categorical imperative in *Critique of Pure Reason* and *Groundwork of the Metaphysics of Morals*. |
+| 5 | **Friedrich Nietzsche** | 19th c., Germany | Critiqued morality and religion; famous for “God is dead” and *Thus Spoke Zarathustra*. |
+| 6 | **Simone de Beauvoir** | 20th c., France | Pioneer of existentialist feminism; author of *The Second Sex*. |
+| 7 | **Confucius (Kong Zi)** | 5th c. BC, China | Founder of Confucianism; emphasized ethics of relationships, ritual, and good governance. |
+| 8 | **John Stuart Mill** | 19th c., United Kingdom | Advocate of utilitarianism and liberty; wrote *On Liberty* and *Utilitarianism*. |
+| 9 | **David Hume** | 18th c., Scotland | Empiricist skeptic; known for his analysis of causation and the problem of induction. |
+|10 | **Martha Nussbaum** | Contemporary, United States | Works on capabilities approach, emotions, and ethics; author of *The Fragility of Goodness* and *Creating Capabilities*. |
+These thinkers span a range of philosophical traditions—Western, Eastern, ancient, modern, and contemporary—so you can explore whichever area interests you most. Let me know if you’d like a deeper dive into any of them!</t>
+        </is>
+      </c>
+      <c r="Y62" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>73</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>619</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>692</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>6.063</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>tel me 10 phyloshper</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>tel me 10 phyloshper</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>69b8d528-b76a-46aa-864d-773236f0959b</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:45:58+00:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V63" t="b">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Here are 10 of the most influential philosophers in history, spanning ancient to modern times and diverse traditions:
+1. **Socrates** (c. 470–399 BCE) – Classical Greek philosopher known for the Socratic method, questioning assumptions, and focusing on ethics and virtue.
+2. **Plato** (c. 428–348 BCE) – Student of Socrates, wrote *The Republic*, founded the Academy in Athens, and explored forms, justice, and the ideal state.
+3. **Aristotle** (384–322 BCE) – Student of Plato, tutor to Alexander the Great; pioneered formal logic, studied biology, and wrote extensively on ethics, metaphysics, and politics.
+4. **René Descartes** (1596–1650) – French mathematician and philosopher; father of modern rationalism, famous for *"Cogito, ergo sum"* ("I think, therefore I am").
+5. **Immanuel Kant** (1724–1804) – German philosopher who revolutionized epistemology and ethics; author of *Critique of Pure Reason* and the categorical imperative.
+6. **Friedrich Nietzsche** (1844–1900) – German philosopher who critiqued morality, religion, and culture; introduced concepts like the "will to power" and the "Übermensch."
+7. **John Stuart Mill** (1806–1873) – British philosopher and political economist; leading figure in utilitarianism and a defender of individual liberty in *On Liberty*.
+8. **Confucius** (551–479 BCE) – Ancient Chinese thinker whose teachings on morality, social relationships, justice, and governance shaped East Asian culture for millennia.
+9. **Jean-Paul Sartre** (1905–1980) – French existentialist philosopher; argued that *"existence precedes essence"* and emphasized radical freedom and responsibility.
+10. **Simone de Beauvoir** (1908–1986) – French existentialist, feminist theorist, and writer; best known for *The Second Sex*, a foundational text in modern feminism.
+Let me know if you'd like deeper info on any of them!</t>
+        </is>
+      </c>
+      <c r="Y63" t="n">
+        <v>1857</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1307</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1332</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>51.732</v>
+      </c>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>tel me 10 phyloshper</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>tel me 10 phyloshper</t>
         </is>
       </c>
     </row>

--- a/logs/run_log.xlsx
+++ b/logs/run_log.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH63"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9755,11 +9755,6 @@
           <t>custom</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>nemotron</t>
@@ -9785,7 +9780,6 @@
           <t>none</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
         <v>1</v>
       </c>
@@ -9847,7 +9841,6 @@
       <c r="AC63" t="n">
         <v>51.732</v>
       </c>
-      <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr">
         <is>
           <t>v0.9</t>
@@ -9866,6 +9859,326 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>tel me 10 phyloshper</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>86d6575b-67ea-465a-9eb0-cd1088c32630</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:52:42+00:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>nemotron</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V64" t="b">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>No, from a scientific and physical standpoint, a **shadow is not a physical entity**.
+Here's why:
+- **It's an optical effect**: A shadow is a dark area or shape created when an object blocks light rays from a source. It's not "made of matter" — it's essentially the *absence* of light in a particular space.
+- **No mass or matter**: Physical entities have mass, occupy space with tangible stuff, and are composed of atoms or molecules. A shadow has none of these.
+- **No energy or momentum**: While light carries energy and momentum, a shadow itself is simply a region where that light is blocked. It doesn't carry or possess energy in the way a physical object does.
+- **Can be projected, but isn't an object**: You can cast a shadow on a wall, screen, or floor, and the shape can be large, detailed, and move — but the shadow itself is a pattern of darkness, not a thing you can touch, weigh, or move independently of the object blocking the light.
+**Edge cases (often confused with "physicality"):** 
+- In intense laser or thermal contexts, the *lack* of radiation in a shadow region can create a measurable temperature or pressure difference, but the shadow remains an optical phenomenon, not a material object.
+- Some quantum optics experiments have mapped "single-photon shadows," but these still describe light-blocking effects, not matter.
+**In short:** A shadow is a visual phenomenon caused by light obstruction, not a physical object or entity.</t>
+        </is>
+      </c>
+      <c r="Y64" t="n">
+        <v>1459</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>992</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1014</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>14.203</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is shadow physcial entity?
+</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is shadow physcial entity?
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>763022ca-1d27-4fe3-9b2f-f594856f97c8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-13T12:52:42+00:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>gpt_oss</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>4096</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="V65" t="b">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>**Short answer:**  
+No – a shadow is not a physical object. It is a region where light (or another kind of radiation) is blocked, so it is the *absence* of photons rather than something that has mass, charge, or a material structure you can touch.
+---
+## Why a shadow isn’t “stuff”
+| Property | What a physical object has | What a shadow has |
+|----------|---------------------------|-------------------|
+| **Matter** (atoms, molecules) | Yes – electrons, nuclei, etc. | No – no particles are “inside” the shadow itself. |
+| **Mass / weight** | Yes – you can weigh it. | Zero – a shadow contributes no gravitational pull. |
+| **Temperature (intrinsic)** | Can be hot or cold because of its material. | No intrinsic temperature; any temperature change comes from the surface that is illuminated (or not). |
+| **Ability to exert forces directly** | Can push, pull, collide, etc. | Cannot push or collide; it can only affect things indirectly by changing the light that reaches them. |
+| **Observable by touch** | Yes – you can feel it. | No – you can’t feel a shadow itself; you only feel the surface that is in shade. |
+In everyday language we say a shadow “covers” a wall, but what’s really happening is:
+1. **Light rays (photons) travel in straight lines** from a source (the Sun, a lamp, etc.).  
+2. **An opaque object blocks some of those rays**.  
+3. **Behind the object, in the geometric region that would have received those rays, the light intensity drops**. That low‑intensity region is what we call a shadow.
+So a shadow is a *pattern* in the distribution of light, not a collection of particles.
+---
+## The physics behind a shadow
+### Classical picture (geometric optics)
+- **Light as rays:** In the ray model, light consists of many straight‑line paths. An object casts a shadow by simply not letting some of those rays pass.
+- **Umbra and penumbra:**  
+  - **Umbra** – the darkest part where *all* direct rays are blocked.  
+  - **Penumbra** – the lighter halo where only part of the source is hidden (important for extended light sources like the Sun).
+- The shape of the shadow is essentially the *silhouette* of the object projected onto the surface where the light is being measured.
+### Wave picture (physical optics)
+- Light is an electromagnetic wave. When an object blocks part of the wavefront, the wave behind the object interferes with itself, creating diffraction patterns.
+- The **Fresnel diffraction** at the edge of a shadow can produce a faint bright fringe (the “Poisson spot”) that a purely geometric model would miss. This shows that the *edges* of a shadow have a subtle wave‑nature, but the interior is still just a region of reduced intensity.
+### Quantum picture
+- Light consists of photons, quantum packets of energy. A photon either goes around the object or is absorbed/scattered by it. The probability distribution of where photons arrive at a screen is what we see as brightness.
+- In an experiment with single photons, you will still get a “shadow” pattern when you compile many detection events, even though each photon is indivisible. The shadow is still a statistical absence of detections, not a material thing.
+---
+## Can a shadow have *effects* that feel “physical”?
+Yes, indirectly:
+| Effect | How it arises | Why it’s not the shadow itself |
+|--------|--------------|--------------------------------|
+| **Cooling of a surface** | Less light → fewer photons absorbed → less heating. | The surface gets cooler; the shadow is just the region of reduced illumination. |
+| **Shadow‑induced wind (e.g., in deserts)** | Sun heats the ground; a passing cloud creates a temporary “shadow” that cools the air, generating a pressure gradient. | The wind is due to temperature differences in the air, not because the shadow pushes anything. |
+| **Solar eclipses affecting temperature &amp; animal behavior** | The Moon blocks the Sun → rapid temperature drop. | Again, it’s the reduction in solar photons, not a “thing” moving across the Earth. |
+| **Detection of hidden objects** (e.g., X‑ray or gamma‑ray imaging) | Radiation is absorbed by dense material; the detector sees a “shadow” in the radiation map. | The detector sees a pattern of missing photons; the hidden object is the physical entity, not the shadow. |
+These phenomena illustrate that while a shadow can *cause* observable changes, those changes are mediated by the *real* matter (the surface, the air, the instrument) that is receiving fewer photons.
+---
+## Edge cases: “Shadows” of non‑light entities
+Because “shadow” technically means “absence of something,” the concept can be extended:
+| Kind of “shadow” | What’s being blocked | How it’s observed |
+|------------------|----------------------|-------------------|
+| **Gravitational lensing “shadow”** (e.g., the black‑hole shadow captured by the Event Horizon Telescope) | Light bent or captured by a massive object’s gravity | A dark region in the image of surrounding emission. It’s still a lack of photons, not a solid object. |
+| **Neutrino shadow** (e.g., Earth blocks cosmic‑ray neutrinos) | High‑energy neutrinos are absorbed by Earth’s dense core | Detectors see fewer neutrinos from directions that pass through the Earth. |
+| **Acoustic shadow** (e.g., sonar “shadow zone” behind a steep seafloor) | Sound waves are blocked/reflected | Sonar receivers see a drop in signal strength. Again, it’s a reduction in wave intensity, not a physical obstacle. |
+These illustrate the universality of the “shadow” idea: any wave or particle flux can have a region of reduced intensity behind an obstacle, but the shadow itself never gains mass or solidity.
+---
+## Common misconceptions
+| Misconception | Why it’s wrong |
+|---------------|----------------|
+| *A shadow can be “touched” or “grabbed.”* | You can only touch the surface that is in shade; the shadow is just the lack of light on that surface. |
+| *Shadows have weight because they block light.* | Photons have momentum, so a beam of light exerts a tiny pressure (radiation pressure). The *blockage* of photons can change how that pressure is distributed, but the shadow does not itself carry that pressure. |
+| *If I move a light source, the shadow moves, so it must be a thing.* | The shadow moves because the geometry of which rays reach which points changes. No material is being displaced. |
+| *A shadow is “dark matter.”* | Dark matter refers to an unseen form of matter that has gravitational effects. A shadow is simply empty space lacking photons; it has no mass or gravitational influence. |
+---
+## Bottom line
+- **A shadow is a pattern of reduced illumination, not a material entity.**  
+- It has **no mass, no charge, no temperature of its own**, and you cannot interact with it directly except through the objects that create it or the surfaces that receive less light.  
+- In physics, we treat a shadow as a **boundary condition** on the electromagnetic (or other) field, not as a particle or a substance.
+If you’re curious about a particular type of shadow—say, the “shadow” a planet casts on starlight in exoplanet transit observations, or the subtle diffraction fringes around a lunar eclipse—let me know and we can dive into the details!</t>
+        </is>
+      </c>
+      <c r="Y65" t="n">
+        <v>7201</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1806</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1877</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>30.337</v>
+      </c>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>v0.9</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>69bf2e75af30f76bd2099a7d048c3264a261372d736b66dda1ab813a7f623884</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is shadow physcial entity?
+</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is shadow physcial entity?
+</t>
         </is>
       </c>
     </row>
